--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20240401_20241001.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20240401_20241001.xlsx
@@ -1053,37 +1053,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>BASF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60.48387096774194</v>
+        <v>55.64516129032258</v>
       </c>
       <c r="C15" t="n">
-        <v>39.51612903225806</v>
+        <v>44.35483870967742</v>
       </c>
       <c r="D15" t="n">
-        <v>54.92910359602061</v>
+        <v>94.00538262733271</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>INE226A01021</t>
+          <t>INE373A01013</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>-20.96774193548387</v>
+        <v>-11.29032258064516</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="I15" t="n">
         <v>69</v>
       </c>
       <c r="J15" t="n">
-        <v>1845.1</v>
+        <v>7385.25</v>
       </c>
       <c r="K15" t="n">
         <v>14</v>
@@ -1097,37 +1097,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BASF</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>55.64516129032258</v>
+        <v>60.48387096774194</v>
       </c>
       <c r="C16" t="n">
-        <v>44.35483870967742</v>
+        <v>39.51612903225806</v>
       </c>
       <c r="D16" t="n">
-        <v>94.00538262733271</v>
+        <v>54.92910359602061</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>INE373A01013</t>
+          <t>INE226A01021</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>-11.29032258064516</v>
+        <v>-20.96774193548387</v>
       </c>
       <c r="H16" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>69</v>
       </c>
       <c r="J16" t="n">
-        <v>7385.25</v>
+        <v>1845.1</v>
       </c>
       <c r="K16" t="n">
         <v>15</v>
